--- a/artfynd/A 36898-2023 artfynd.xlsx
+++ b/artfynd/A 36898-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36898-2023 artfynd.xlsx
+++ b/artfynd/A 36898-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4168419</v>
+        <v>4215247</v>
       </c>
       <c r="B2" t="n">
-        <v>95510</v>
+        <v>95518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>450 m N om St Mörteråstjärnet, Röane, Boh</t>
+          <t>Ravin 450 m N om St Mörteråstjärnet, Röane, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>313691.5710942657</v>
+        <v>313661.9915719467</v>
       </c>
       <c r="R2" t="n">
-        <v>6521975.647836233</v>
+        <v>6521955.274640297</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>rasmark, klippstup</t>
+          <t>källdråg, skogskärr</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -789,123 +789,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>4215247</v>
-      </c>
-      <c r="B3" t="n">
-        <v>95518</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Ravin 450 m N om St Mörteråstjärnet, Röane, Boh</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>313661.9915719467</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6521955.274640297</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Munkedal</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Krokstad</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>1999-08-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>1999-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>källdråg, skogskärr</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Föreningen Bohusläns Flora</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Föreningen Bohusläns Flora</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
